--- a/hollin-renewal/image-replacement-list.xlsx
+++ b/hollin-renewal/image-replacement-list.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I160"/>
+  <dimension ref="A1:I189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -619,7 +618,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -662,7 +660,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -705,7 +702,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -748,7 +744,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -791,7 +786,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -834,7 +828,6 @@
           <t>2560px 이상</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -877,7 +870,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -920,7 +912,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -963,7 +954,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1006,7 +996,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1049,7 +1038,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1092,7 +1080,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1135,7 +1122,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1178,7 +1164,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1221,7 +1206,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1264,7 +1248,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1307,7 +1290,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1350,93 +1332,92 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>1 (우선)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>p26-0.jpg</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>758×426</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>SCL INTERNATIONAL CONFERENCE</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>SCL 40주년 국제학술대회</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>홈 프로젝트 목록, WORK 목록, 상세 대표 이미지</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>1 (우선)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>p26-1.jpg</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>758×426</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>PARTNER CONNECT</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>한양대학교 PARTNER CONNECT</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>홈 프로젝트 목록, WORK 목록, 상세 대표 이미지</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1479,7 +1460,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1522,7 +1502,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1565,7 +1544,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1608,7 +1586,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1651,7 +1628,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1904,7 +1880,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1947,7 +1922,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1990,7 +1964,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2033,7 +2006,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2076,7 +2048,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2119,7 +2090,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2162,7 +2132,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2205,7 +2174,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2248,7 +2216,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2291,7 +2258,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2334,7 +2300,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2377,7 +2342,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2420,7 +2384,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2463,7 +2426,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2506,7 +2468,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2549,7 +2510,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2592,7 +2552,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2635,7 +2594,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2678,7 +2636,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2721,7 +2678,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2764,7 +2720,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2807,7 +2762,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2850,7 +2804,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2893,7 +2846,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2936,7 +2888,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2979,7 +2930,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3022,7 +2972,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3065,7 +3014,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3108,7 +3056,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3151,7 +3098,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3194,7 +3140,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3237,7 +3182,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3280,7 +3224,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3323,7 +3266,6 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3366,3920 +3308,5166 @@
           <t>1920px 이상</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-1.jpg</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>SCL헬스케어 홍보 영상</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>SCL헬스케어 홍보 영상</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-10.jpg</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>2022 발달장애인대회 홍보 영상</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>2022 발달장애인대회 홍보 영상</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-11.jpg</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>㈜제이준 홍보 영상 ( 제품 &amp;회사 홍보 영상 )</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>㈜제이준 홍보 영상 ( 제품 &amp;회사 홍보 영상 )</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-12.jpg</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>1920×867</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>다케다제약 홍보 영상</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>다케다제약 홍보 영상</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-13.jpg</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>서울시립대학교 청년UP플랫폼 공간 홍보 영상</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>서울시립대학교 청년UP플랫폼 공간 홍보 영상</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-14.jpg</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 메이커스페이스 공간 홍보 영상</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 메이커스페이스 공간 홍보 영상</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-15.jpg</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>1920×847</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업해봄 홍보 영상</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업해봄 홍보 영상</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-2.jpg</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>㈜스탠스 홍보 영상</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>㈜스탠스 홍보 영상</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-3.jpg</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>로보로보랜드아이키로 홍보 영상</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>로보로보랜드아이키로 홍보 영상</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-4.jpg</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>㈜로보로보랜드 홍보 영상</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>㈜로보로보랜드 홍보 영상</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-5.jpg</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>로보링크코드론미니(ver1,2) 홍보 영상</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>로보링크코드론미니(ver1,2) 홍보 영상</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-6.jpg</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>㈜에코제로실버테라피 제품 홍보 영상</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>㈜에코제로실버테라피 제품 홍보 영상</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-7.jpg</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>㈜에코제로아홉테라피 제품 홍보 영상</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>㈜에코제로아홉테라피 제품 홍보 영상</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-8.jpg</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>1920×960</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>인덕대학교 창업동아리 CARE PET 어플 홍보 영상</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>인덕대학교 창업동아리 CARE PET 어플 홍보 영상</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>portfolio-18-9.jpg</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>인덕대학교 창업동아리 EDA 패션 스케치 홍보 영상</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>인덕대학교 창업동아리 EDA 패션 스케치 홍보 영상</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>portfolio-19-1.jpg</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>408×230</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>2560×1440</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업지원단 창퀴즈온더블럭(2편)</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업지원단 창퀴즈온더블럭(2편)</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>portfolio-19-2.jpg</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>408×230</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업지원단 창업술집토크(2편)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업지원단 창업술집토크(2편)</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>portfolio-19-3.jpg</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>408×230</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업지원단 창업동아리 ‘아툴’ 브이로그 (1편)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업지원단 창업동아리 ‘아툴’ 브이로그 (1편)</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>portfolio-19-4.jpg</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>408×230</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업지원단 홍보 인포그래픽 (1편)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업지원단 홍보 인포그래픽 (1편)</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>portfolio-19-5.jpg</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>408×230</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업지원단 창업보육센터 홍보 영상 (6편)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>서울과학 기술 대학교 창업지원단 창업보육센터 홍보 영상 (6편)</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>portfolio-19-6.jpg</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>408×230</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>제네시스 인포그래픽 홍보 영상</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>제네시스 인포그래픽 홍보 영상</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>portfolio-19-7.jpg</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>408×230</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>제네시스‘작은사람들‘ 홍보 영상</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>제네시스‘작은사람들‘ 홍보 영상</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>portfolio-19-8.jpg</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>408×230</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>‘미니언즈여행가다＇</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>‘미니언즈여행가다＇</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-1.jpg</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 40주년 국제학술대회 1부 오프닝 영상</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 40주년 국제학술대회 1부 오프닝 영상</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-10.jpg</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>1280×691</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>SCL 제주의원 개원식 기념 영상</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>SCL 제주의원 개원식 기념 영상</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-11.jpg</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 40주년 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 40주년 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-12.jpg</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 40주년그룹사 기념 영상</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 40주년그룹사 기념 영상</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-13.jpg</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>연세대총동문회제1,2회 보건의료분과위원회 포럼 오프닝 영상</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>연세대총동문회제1,2회 보건의료분과위원회 포럼 오프닝 영상</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-14.jpg</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>BD APM 오프닝 영상</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>BD APM 오프닝 영상</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-15.jpg</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>BD APM Patient Story 영상</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>BD APM Patient Story 영상</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-2.jpg</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 40주년 국제학술대회 2부 오프닝 영상</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 40주년 국제학술대회 2부 오프닝 영상</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-3.jpg</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>혜산기금연구보고및정부정책 토론회 오프닝 영상</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>혜산기금연구보고및정부정책 토론회 오프닝 영상</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-4.jpg</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 41주년 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 41주년 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-5.jpg</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>TDI 강원관광도로선포식 오프닝 영상</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>TDI 강원관광도로선포식 오프닝 영상</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-6.jpg</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>TDI 강원관광도로선포식 퍼포먼스 영상</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>TDI 강원관광도로선포식 퍼포먼스 영상</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-7.jpg</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>TDI 대한민국테마여행 10선 포럼 행사 오프닝</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>TDI 대한민국테마여행 10선 포럼 행사 오프닝</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-8.jpg</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>1920×1056</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>대한민국의학한림원제2회 보건의료 포럼 오프닝 영상</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>대한민국의학한림원제2회 보건의료 포럼 오프닝 영상</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>portfolio-20-9.jpg</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>SCL 제주의원 개원식 오프닝 영상</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>SCL 제주의원 개원식 오프닝 영상</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-1.jpg</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>BD APM 루핑 영상</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>BD APM 루핑 영상</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-10.jpg</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>1920×899</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>ADA 심포지움 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>ADA 심포지움 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-11.jpg</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>SCL 2022 송년회 오프닝 영상</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>SCL 2022 송년회 오프닝 영상</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-12.jpg</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>SCL 2023 송년회 오프닝 영상</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>SCL 2023 송년회 오프닝 영상</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-13.jpg</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>사단법인조각보 오프닝 영상</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>사단법인조각보 오프닝 영상</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-14.jpg</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>2022 화물운전자의 날 행사 기념 영상</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>2022 화물운전자의 날 행사 기념 영상</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-15.jpg</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>TIPS 엔젤투자협회 사업설명회</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>TIPS 엔젤투자협회 사업설명회</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-2.jpg</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>제19회서울지역창업기업 만남의장 오프닝 영상</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>제19회서울지역창업기업 만남의장 오프닝 영상</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-3.jpg</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>제18회서울지역창업기업 만남의장 오프닝 영상</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>제18회서울지역창업기업 만남의장 오프닝 영상</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-4.jpg</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>SCL 39주년 오프닝 영상</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>SCL 39주년 오프닝 영상</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-5.jpg</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>SCL 39주년 기념 영상</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>SCL 39주년 기념 영상</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-6.jpg</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>1664×1050</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>NOVARTIS 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>NOVARTIS 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-7.jpg</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>여성가족부3·1절 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>여성가족부3·1절 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-8.jpg</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>서울돈화문국악당개관축제및 개관식 기념 영상</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>서울돈화문국악당개관축제및 개관식 기념 영상</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>portfolio-21-9.jpg</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>1920×1025</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>동아ST 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>동아ST 행사 오프닝 영상</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-1.jpg</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>SCL 40주년 기념 국제학술대회 스케치 영상</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>SCL 40주년 기념 국제학술대회 스케치 영상</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-10.jpg</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>한양대학교 토크 콘서트 어쩌다창업 스케치 영상</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>한양대학교 토크 콘서트 어쩌다창업 스케치 영상</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-11.jpg</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>가천대 창업지원단 스타트업 네트워킹데이 스케치 영상</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>가천대 창업지원단 스타트업 네트워킹데이 스케치 영상</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-12.jpg</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>한밭대학교 X-CORPS 경진대회 스케치 영상</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>한밭대학교 X-CORPS 경진대회 스케치 영상</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-13.jpg</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>연세대제1,2회 보건의료 포럼 스케치 영상</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>연세대제1,2회 보건의료 포럼 스케치 영상</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-14.jpg</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>2560×1440</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>제19회서울지역창업기업 만남의장 스케치 영상</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>제19회서울지역창업기업 만남의장 스케치 영상</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-15.jpg</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>1920×810</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>새벽교회하나님땡큐 콘서트 스케치 영상</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>새벽교회하나님땡큐 콘서트 스케치 영상</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-2.jpg</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>SCL40주년 창립 기념 식 스케치 영상</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>SCL40주년 창립 기념 식 스케치 영상</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-3.jpg</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>한양대PARTNER CONNECT 스케치 영상</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>한양대PARTNER CONNECT 스케치 영상</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-4.jpg</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>1280×691</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>SCL 제주의원 개원식 스케치 영상</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>SCL 제주의원 개원식 스케치 영상</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-5.jpg</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>BD APM KOREA 스케치 영상</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>BD APM KOREA 스케치 영상</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-6.jpg</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>SCL 송년회 스케치 영상 (22, 23, 24, 25년)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>SCL 송년회 스케치 영상 (22, 23, 24, 25년)</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-7.jpg</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>TDI제주동백마을레스토랑 스케치 영상</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>TDI제주동백마을레스토랑 스케치 영상</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-8.jpg</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>TDI 제주저지마을레스토랑 스케치 영상</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>TDI 제주저지마을레스토랑 스케치 영상</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>portfolio-22-9.jpg</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>IDB’S PROJECT 스케치 영상</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>IDB’S PROJECT 스케치 영상</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-1.jpg</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 세진회 새해 인사의 밤 스케치 영상</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 세진회 새해 인사의 밤 스케치 영상</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-10.jpg</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>2025 TIPS 사업설명회 영상</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>2025 TIPS 사업설명회 영상</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-11.jpg</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>K-ART 문신사법허용 스케치 영상</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>K-ART 문신사법허용 스케치 영상</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-12.jpg</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>KEXPO KART FAIR 스케치 영상</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>KEXPO KART FAIR 스케치 영상</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-13.jpg</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>연세대학교 의과대학 7985 동기회 스케치 영상</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>연세대학교 의과대학 7985 동기회 스케치 영상</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-14.jpg</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>SCL 그룹오티즘레이스 스케치 영상</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>SCL 그룹오티즘레이스 스케치 영상</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-15.jpg</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>솔빛 시스템 BRIDGE 기술 소개 영상</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>솔빛 시스템 BRIDGE 기술 소개 영상</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-2.jpg</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 세진회 새해 인사의 밤하이라이트 영상</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 세진회 새해 인사의 밤하이라이트 영상</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-3.jpg</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>1920×986</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>SCL 광주의원 개원식 오프닝 영상</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>SCL 광주의원 개원식 오프닝 영상</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-4.jpg</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>SCL 광주의원 개원식 스케치 영상</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>SCL 광주의원 개원식 스케치 영상</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-5.jpg</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>1280×683</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>인천적십자병원공공보건의료 협력체계구축사업슬라이드 영상</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>인천적십자병원공공보건의료 협력체계구축사업슬라이드 영상</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-6.jpg</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>인천적십자병원 치매노인교육 영상</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>인천적십자병원 치매노인교육 영상</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-7.jpg</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>1280×720</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>교체 완료(1280px)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>꽃스러움‘통하다’ 전시회 스케치 영상</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>꽃스러움‘통하다’ 전시회 스케치 영상</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-8.jpg</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 42주년 오프닝 영상</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>SCL 창립 42주년 오프닝 영상</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>portfolio-23-9.jpg</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>JW PROMISE 창립 80주년 오프닝 영상</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>JW PROMISE 창립 80주년 오프닝 영상</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>portfolio-24-1.jpg</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Hanyang Startup Summit 스케치 영상</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Hanyang Startup Summit 스케치 영상</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>portfolio-24-2.jpg</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 송년회 오프닝 영상</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 송년회 오프닝 영상</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>portfolio-24-3.jpg</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 송년회 루핑 영상</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 송년회 루핑 영상</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>portfolio-24-4.jpg</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>1920×939</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 송년회 ‘한해를돌아보며’ 영상</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 송년회 ‘한해를돌아보며’ 영상</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>portfolio-24-5.jpg</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 송년회 ‘복면가왕’ 티저 영상</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 송년회 ‘복면가왕’ 티저 영상</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>portfolio-24-6.jpg</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 송년회 ‘복면가왕’ 참가자 티저 영상</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>SCL 2025 송년회 ‘복면가왕’ 참가자 티저 영상</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>portfolio-24-7.jpg</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>SCL 2026 세진회 새해 인사의 밤 스케치 영상</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>SCL 2026 세진회 새해 인사의 밤 스케치 영상</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>portfolio-24-8.jpg</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>314×178</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>교체 필요</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>1920×1053</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>2026 TIPS 사업설명회 영상</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>2026 TIPS 사업설명회 영상</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>WORK 목록, 상세 대표 이미지</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>1920px 이상</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>project-archive-18-2-2.jpg</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>㈜스탠스 홍보 영상</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>㈜스탠스 홍보 영상</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>상세 갤러리</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>project-archive-19-1-2.jpg</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>2560×1440</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>서울과학 기술 대학교 창업지원단 창퀴즈온더블럭(2편)</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>서울과학 기술 대학교 창업지원단 창퀴즈온더블럭(2편)</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>상세 갤러리</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-1.jpg</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>BD APM Kick off Ceremony 행사 운영 총괄</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>BD APM Kick off Ceremony 행사 운영 총괄</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-2.jpg</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>TEXPO대한문신사박람회및컨퍼런스 운영</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>TEXPO대한문신사박람회및컨퍼런스 운영</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-3.jpg</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>대한민국의학한림원 학술 포럼 운영</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>대한민국의학한림원 학술 포럼 운영</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-4.jpg</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>국회의원회관조화로움 플라워 전시회 운영</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>국회의원회관조화로움 플라워 전시회 운영</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-5.jpg</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>SCL MIT(introduction toquantum computing) 강연 총괄</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>SCL MIT(introduction toquantum computing) 강연 총괄</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-7.jpg</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>한양대학교 토크 콘서트 ‘어쩌다창업‘</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>한양대학교 토크 콘서트 ‘어쩌다창업‘</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-8.jpg</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>남양주시 청소년회관 정책발표대회 음향 , 시스템 총괄</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>남양주시 청소년회관 정책발표대회 음향 , 시스템 총괄</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-9.jpg</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>SCL 광주의원 개원식</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>SCL 광주의원 개원식</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-10.jpg</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>1920×912</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>고려대학교83학번 홈커밍데이 시스템 총괄</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>고려대학교83학번 홈커밍데이 시스템 총괄</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-12.jpg</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>서울대학교병원PATOS 국제 심포지엄 송출</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>서울대학교병원PATOS 국제 심포지엄 송출</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-13.jpg</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>서울대학교병원 급성심장정지 구급품질 향상 워크숍 송출</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>서울대학교병원 급성심장정지 구급품질 향상 워크숍 송출</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-14.jpg</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>김정식재즈밴드 갤러리 콘서트 음향 , 영상</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>김정식재즈밴드 갤러리 콘서트 음향 , 영상</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-15.jpg</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>홍대코코넛박스RADI 단독 공연 음향 , 시스템 총괄</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>홍대코코넛박스RADI 단독 공연 음향 , 시스템 총괄</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>project-live-26-17.jpg</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>한양대학교 어쩌다창잘알토크 콘서트 송출</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>한양대학교 어쩌다창잘알토크 콘서트 송출</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-20.jpg</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>1920×992</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>이다온 단독 콘서트 시스템 총괄</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>이다온 단독 콘서트 시스템 총괄</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-21.jpg</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>제19회서울지역창업기업 만남의장</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>제19회서울지역창업기업 만남의장</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-22.jpg</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>1920×810</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>새벽교회‘땡큐 콘서트 ‘ 시스템 총괄</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>새벽교회‘땡큐 콘서트 ‘ 시스템 총괄</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-23.jpg</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>SCL 제주의원 개원식</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>SCL 제주의원 개원식</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-24.jpg</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>SCL 39주년 창립 기념 식 행사</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>SCL 39주년 창립 기념 식 행사</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-26.jpg</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>한국스포츠정책과학원체육문화 행사</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>한국스포츠정책과학원체육문화 행사</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-27.jpg</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>대한민국구급활동경연대회 음향 , 영상</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>대한민국구급활동경연대회 음향 , 영상</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-32.jpg</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>제18회서울지역창업기업 만남의장</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>제18회서울지역창업기업 만남의장</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-33.jpg</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>TDI강원관광도로선포식</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>TDI강원관광도로선포식</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-36.jpg</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>숭실대학교예비창업패키지역량교육 음향 , 송출</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>숭실대학교예비창업패키지역량교육 음향 , 송출</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-37.jpg</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>IDB’S Project 행사 총괄</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>IDB’S Project 행사 총괄</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-38.jpg</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>대한항암요법연구회 심포지엄</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>대한항암요법연구회 심포지엄</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>project-live-27-39.jpg</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>1920×1080</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>충분</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>2021 야놀자 송년회 행사 송출</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>2021 야놀자 송년회 행사 송출</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>WORK 목록, 상세 대표 이미지</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>1920px 이상</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I160"/>
